--- a/data/Etex_Australia_MA_Showcase_v5_bc.xlsx
+++ b/data/Etex_Australia_MA_Showcase_v5_bc.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="14_{613D3431-BE0B-49C9-BBFB-3D64876005DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A138A7A-F8CE-4D1B-83EC-C20D683A31C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="881" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1785" yWindow="1365" windowWidth="22980" windowHeight="13935" tabRatio="881" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etex Brand Identity" sheetId="1" state="hidden" r:id="rId1"/>
@@ -5485,40 +5485,68 @@
     <xf numFmtId="173" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="173" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5526,22 +5554,6 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5551,8 +5563,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5560,18 +5572,12 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5589,9 +5595,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5602,21 +5605,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5631,9 +5634,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5651,6 +5651,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6162,32 +6166,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>767</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="297" t="s">
+      <c r="A3" s="288" t="s">
         <v>768</v>
       </c>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="286"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
@@ -6262,19 +6266,19 @@
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="297" t="s">
+      <c r="A12" s="288" t="s">
         <v>776</v>
       </c>
-      <c r="B12" s="285"/>
-      <c r="C12" s="285"/>
-      <c r="D12" s="285"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="285"/>
-      <c r="G12" s="285"/>
-      <c r="H12" s="285"/>
-      <c r="I12" s="285"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="285"/>
+      <c r="B12" s="286"/>
+      <c r="C12" s="286"/>
+      <c r="D12" s="286"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="286"/>
+      <c r="G12" s="286"/>
+      <c r="H12" s="286"/>
+      <c r="I12" s="286"/>
+      <c r="J12" s="286"/>
+      <c r="K12" s="286"/>
     </row>
     <row r="13" spans="1:16" ht="25.5" customHeight="1">
       <c r="A13" s="33" t="s">
@@ -6497,86 +6501,86 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="72.75" customHeight="1">
-      <c r="A21" s="322" t="s">
+      <c r="A21" s="324" t="s">
         <v>794</v>
       </c>
-      <c r="B21" s="285"/>
-      <c r="C21" s="285"/>
-      <c r="D21" s="285"/>
-      <c r="E21" s="285"/>
-      <c r="F21" s="285"/>
-      <c r="G21" s="285"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="285"/>
-      <c r="J21" s="285"/>
-      <c r="K21" s="285"/>
+      <c r="B21" s="286"/>
+      <c r="C21" s="286"/>
+      <c r="D21" s="286"/>
+      <c r="E21" s="286"/>
+      <c r="F21" s="286"/>
+      <c r="G21" s="286"/>
+      <c r="H21" s="286"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="286"/>
+      <c r="K21" s="286"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="285"/>
-      <c r="B22" s="285"/>
-      <c r="C22" s="285"/>
-      <c r="D22" s="285"/>
-      <c r="E22" s="285"/>
-      <c r="F22" s="285"/>
-      <c r="G22" s="285"/>
-      <c r="H22" s="285"/>
-      <c r="I22" s="285"/>
-      <c r="J22" s="285"/>
-      <c r="K22" s="285"/>
+      <c r="A22" s="286"/>
+      <c r="B22" s="286"/>
+      <c r="C22" s="286"/>
+      <c r="D22" s="286"/>
+      <c r="E22" s="286"/>
+      <c r="F22" s="286"/>
+      <c r="G22" s="286"/>
+      <c r="H22" s="286"/>
+      <c r="I22" s="286"/>
+      <c r="J22" s="286"/>
+      <c r="K22" s="286"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="285"/>
-      <c r="B23" s="285"/>
-      <c r="C23" s="285"/>
-      <c r="D23" s="285"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="285"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="285"/>
+      <c r="A23" s="286"/>
+      <c r="B23" s="286"/>
+      <c r="C23" s="286"/>
+      <c r="D23" s="286"/>
+      <c r="E23" s="286"/>
+      <c r="F23" s="286"/>
+      <c r="G23" s="286"/>
+      <c r="H23" s="286"/>
+      <c r="I23" s="286"/>
+      <c r="J23" s="286"/>
+      <c r="K23" s="286"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="285"/>
-      <c r="B24" s="285"/>
-      <c r="C24" s="285"/>
-      <c r="D24" s="285"/>
-      <c r="E24" s="285"/>
-      <c r="F24" s="285"/>
-      <c r="G24" s="285"/>
-      <c r="H24" s="285"/>
-      <c r="I24" s="285"/>
-      <c r="J24" s="285"/>
-      <c r="K24" s="285"/>
+      <c r="A24" s="286"/>
+      <c r="B24" s="286"/>
+      <c r="C24" s="286"/>
+      <c r="D24" s="286"/>
+      <c r="E24" s="286"/>
+      <c r="F24" s="286"/>
+      <c r="G24" s="286"/>
+      <c r="H24" s="286"/>
+      <c r="I24" s="286"/>
+      <c r="J24" s="286"/>
+      <c r="K24" s="286"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="285"/>
-      <c r="B25" s="285"/>
-      <c r="C25" s="285"/>
-      <c r="D25" s="285"/>
-      <c r="E25" s="285"/>
-      <c r="F25" s="285"/>
-      <c r="G25" s="285"/>
-      <c r="H25" s="285"/>
-      <c r="I25" s="285"/>
-      <c r="J25" s="285"/>
-      <c r="K25" s="285"/>
+      <c r="A25" s="286"/>
+      <c r="B25" s="286"/>
+      <c r="C25" s="286"/>
+      <c r="D25" s="286"/>
+      <c r="E25" s="286"/>
+      <c r="F25" s="286"/>
+      <c r="G25" s="286"/>
+      <c r="H25" s="286"/>
+      <c r="I25" s="286"/>
+      <c r="J25" s="286"/>
+      <c r="K25" s="286"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="330" t="s">
+      <c r="A26" s="331" t="s">
         <v>795</v>
       </c>
-      <c r="B26" s="285"/>
-      <c r="C26" s="285"/>
-      <c r="D26" s="285"/>
-      <c r="E26" s="285"/>
-      <c r="F26" s="285"/>
-      <c r="G26" s="285"/>
-      <c r="H26" s="285"/>
-      <c r="I26" s="285"/>
-      <c r="J26" s="285"/>
-      <c r="K26" s="285"/>
+      <c r="B26" s="286"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="286"/>
+      <c r="E26" s="286"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
+      <c r="H26" s="286"/>
+      <c r="I26" s="286"/>
+      <c r="J26" s="286"/>
+      <c r="K26" s="286"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6607,36 +6611,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>796</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="297" t="s">
+      <c r="A3" s="288" t="s">
         <v>797</v>
       </c>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="286"/>
+      <c r="G3" s="286"/>
+      <c r="H3" s="286"/>
     </row>
     <row r="4" spans="1:16" ht="25.5" customHeight="1">
       <c r="A4" s="33" t="s">
@@ -7010,16 +7014,16 @@
       <c r="H21" s="47"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="297" t="s">
+      <c r="A24" s="288" t="s">
         <v>835</v>
       </c>
-      <c r="B24" s="285"/>
-      <c r="C24" s="285"/>
-      <c r="D24" s="285"/>
-      <c r="E24" s="285"/>
-      <c r="F24" s="285"/>
-      <c r="G24" s="285"/>
-      <c r="H24" s="285"/>
+      <c r="B24" s="286"/>
+      <c r="C24" s="286"/>
+      <c r="D24" s="286"/>
+      <c r="E24" s="286"/>
+      <c r="F24" s="286"/>
+      <c r="G24" s="286"/>
+      <c r="H24" s="286"/>
     </row>
     <row r="25" spans="1:8" ht="38.25" customHeight="1">
       <c r="A25" s="33" t="s">
@@ -7157,16 +7161,16 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="297" t="s">
+      <c r="A33" s="288" t="s">
         <v>847</v>
       </c>
-      <c r="B33" s="285"/>
-      <c r="C33" s="285"/>
-      <c r="D33" s="285"/>
-      <c r="E33" s="285"/>
-      <c r="F33" s="285"/>
-      <c r="G33" s="285"/>
-      <c r="H33" s="285"/>
+      <c r="B33" s="286"/>
+      <c r="C33" s="286"/>
+      <c r="D33" s="286"/>
+      <c r="E33" s="286"/>
+      <c r="F33" s="286"/>
+      <c r="G33" s="286"/>
+      <c r="H33" s="286"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="149" t="s">
@@ -7387,38 +7391,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>864</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="297" t="s">
+      <c r="A3" s="288" t="s">
         <v>865</v>
       </c>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="286"/>
+      <c r="G3" s="286"/>
+      <c r="H3" s="286"/>
+      <c r="I3" s="286"/>
+      <c r="J3" s="286"/>
     </row>
     <row r="4" spans="1:16" ht="25.5" customHeight="1">
       <c r="A4" s="33" t="s">
@@ -7590,18 +7594,18 @@
       <c r="J8" s="44"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="297" t="s">
+      <c r="A11" s="288" t="s">
         <v>877</v>
       </c>
-      <c r="B11" s="285"/>
-      <c r="C11" s="285"/>
-      <c r="D11" s="285"/>
-      <c r="E11" s="285"/>
-      <c r="F11" s="285"/>
-      <c r="G11" s="285"/>
-      <c r="H11" s="285"/>
-      <c r="I11" s="285"/>
-      <c r="J11" s="285"/>
+      <c r="B11" s="286"/>
+      <c r="C11" s="286"/>
+      <c r="D11" s="286"/>
+      <c r="E11" s="286"/>
+      <c r="F11" s="286"/>
+      <c r="G11" s="286"/>
+      <c r="H11" s="286"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="286"/>
     </row>
     <row r="12" spans="1:16" ht="25.5" customHeight="1">
       <c r="A12" s="33" t="s">
@@ -7613,15 +7617,15 @@
       <c r="C12" s="33" t="s">
         <v>879</v>
       </c>
-      <c r="D12" s="335" t="s">
+      <c r="D12" s="332" t="s">
         <v>880</v>
       </c>
-      <c r="E12" s="303"/>
-      <c r="F12" s="303"/>
-      <c r="G12" s="303"/>
-      <c r="H12" s="303"/>
-      <c r="I12" s="303"/>
-      <c r="J12" s="289"/>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="295"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="293"/>
     </row>
     <row r="13" spans="1:16" ht="26.25" customHeight="1">
       <c r="A13" s="18" t="s">
@@ -7633,15 +7637,15 @@
       <c r="C13" s="65" t="s">
         <v>882</v>
       </c>
-      <c r="D13" s="332" t="s">
+      <c r="D13" s="335" t="s">
         <v>883</v>
       </c>
-      <c r="E13" s="303"/>
-      <c r="F13" s="303"/>
-      <c r="G13" s="303"/>
-      <c r="H13" s="303"/>
-      <c r="I13" s="303"/>
-      <c r="J13" s="289"/>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="295"/>
+      <c r="I13" s="295"/>
+      <c r="J13" s="293"/>
     </row>
     <row r="14" spans="1:16" ht="26.25" customHeight="1">
       <c r="A14" s="23" t="s">
@@ -7656,12 +7660,12 @@
       <c r="D14" s="333" t="s">
         <v>886</v>
       </c>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
-      <c r="G14" s="303"/>
-      <c r="H14" s="303"/>
-      <c r="I14" s="303"/>
-      <c r="J14" s="289"/>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="295"/>
+      <c r="I14" s="295"/>
+      <c r="J14" s="293"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="18" t="s">
@@ -7673,15 +7677,15 @@
       <c r="C15" s="65" t="s">
         <v>885</v>
       </c>
-      <c r="D15" s="332" t="s">
+      <c r="D15" s="335" t="s">
         <v>888</v>
       </c>
-      <c r="E15" s="303"/>
-      <c r="F15" s="303"/>
-      <c r="G15" s="303"/>
-      <c r="H15" s="303"/>
-      <c r="I15" s="303"/>
-      <c r="J15" s="289"/>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
+      <c r="H15" s="295"/>
+      <c r="I15" s="295"/>
+      <c r="J15" s="293"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="23" t="s">
@@ -7696,12 +7700,12 @@
       <c r="D16" s="333" t="s">
         <v>890</v>
       </c>
-      <c r="E16" s="303"/>
-      <c r="F16" s="303"/>
-      <c r="G16" s="303"/>
-      <c r="H16" s="303"/>
-      <c r="I16" s="303"/>
-      <c r="J16" s="289"/>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="295"/>
+      <c r="I16" s="295"/>
+      <c r="J16" s="293"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="26" t="s">
@@ -7715,29 +7719,29 @@
         <f>IF(B17&gt;=0,"Favourable","Adverse")</f>
         <v>Adverse</v>
       </c>
-      <c r="D17" s="334" t="s">
+      <c r="D17" s="336" t="s">
         <v>892</v>
       </c>
-      <c r="E17" s="303"/>
-      <c r="F17" s="303"/>
-      <c r="G17" s="303"/>
-      <c r="H17" s="303"/>
-      <c r="I17" s="303"/>
-      <c r="J17" s="289"/>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="295"/>
+      <c r="I17" s="295"/>
+      <c r="J17" s="293"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="297" t="s">
+      <c r="A20" s="288" t="s">
         <v>893</v>
       </c>
-      <c r="B20" s="285"/>
-      <c r="C20" s="285"/>
-      <c r="D20" s="285"/>
-      <c r="E20" s="285"/>
-      <c r="F20" s="285"/>
-      <c r="G20" s="285"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="285"/>
-      <c r="J20" s="285"/>
+      <c r="B20" s="286"/>
+      <c r="C20" s="286"/>
+      <c r="D20" s="286"/>
+      <c r="E20" s="286"/>
+      <c r="F20" s="286"/>
+      <c r="G20" s="286"/>
+      <c r="H20" s="286"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="286"/>
     </row>
     <row r="21" spans="1:10" ht="25.5" customHeight="1">
       <c r="A21" s="33" t="s">
@@ -7902,18 +7906,18 @@
       <c r="H26" s="44"/>
     </row>
     <row r="29" spans="1:10" ht="24" customHeight="1">
-      <c r="A29" s="331" t="s">
+      <c r="A29" s="334" t="s">
         <v>910</v>
       </c>
-      <c r="B29" s="303"/>
-      <c r="C29" s="303"/>
-      <c r="D29" s="303"/>
-      <c r="E29" s="303"/>
-      <c r="F29" s="303"/>
-      <c r="G29" s="303"/>
-      <c r="H29" s="303"/>
-      <c r="I29" s="303"/>
-      <c r="J29" s="289"/>
+      <c r="B29" s="295"/>
+      <c r="C29" s="295"/>
+      <c r="D29" s="295"/>
+      <c r="E29" s="295"/>
+      <c r="F29" s="295"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
+      <c r="I29" s="295"/>
+      <c r="J29" s="293"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -7951,30 +7955,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>911</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="311" t="s">
         <v>912</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
     </row>
     <row r="3" spans="1:9" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -8240,17 +8244,17 @@
       <c r="I11" s="86"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="297" t="s">
+      <c r="A14" s="288" t="s">
         <v>934</v>
       </c>
-      <c r="B14" s="285"/>
-      <c r="C14" s="285"/>
-      <c r="D14" s="285"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="285"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="285"/>
+      <c r="B14" s="286"/>
+      <c r="C14" s="286"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="286"/>
+      <c r="I14" s="286"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="108" t="s">
@@ -8458,40 +8462,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>950</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="336" t="s">
+      <c r="A3" s="337" t="s">
         <v>951</v>
       </c>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="286"/>
+      <c r="G3" s="286"/>
+      <c r="H3" s="286"/>
+      <c r="I3" s="286"/>
+      <c r="J3" s="286"/>
+      <c r="K3" s="286"/>
+      <c r="L3" s="286"/>
     </row>
     <row r="4" spans="1:16" ht="25.5" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -9238,32 +9242,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>990</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
     </row>
     <row r="2" spans="1:10" ht="32.1" customHeight="1">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="290" t="s">
         <v>991</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
     </row>
     <row r="3" spans="1:10" ht="32.1" customHeight="1">
       <c r="A3" s="33" t="s">
@@ -10482,18 +10486,18 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A41" s="337" t="s">
+      <c r="A41" s="338" t="s">
         <v>1170</v>
       </c>
-      <c r="B41" s="303"/>
-      <c r="C41" s="303"/>
-      <c r="D41" s="303"/>
-      <c r="E41" s="303"/>
-      <c r="F41" s="303"/>
-      <c r="G41" s="303"/>
-      <c r="H41" s="303"/>
-      <c r="I41" s="303"/>
-      <c r="J41" s="289"/>
+      <c r="B41" s="295"/>
+      <c r="C41" s="295"/>
+      <c r="D41" s="295"/>
+      <c r="E41" s="295"/>
+      <c r="F41" s="295"/>
+      <c r="G41" s="295"/>
+      <c r="H41" s="295"/>
+      <c r="I41" s="295"/>
+      <c r="J41" s="293"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10522,46 +10526,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>1171</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="290" t="s">
         <v>1172</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
     </row>
     <row r="4" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A4" s="297" t="s">
+      <c r="A4" s="288" t="s">
         <v>1173</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -10866,18 +10870,18 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A20" s="313" t="s">
+      <c r="A20" s="289" t="s">
         <v>1228</v>
       </c>
-      <c r="B20" s="285"/>
-      <c r="C20" s="285"/>
-      <c r="D20" s="285"/>
-      <c r="E20" s="285"/>
-      <c r="F20" s="285"/>
-      <c r="G20" s="285"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="285"/>
-      <c r="J20" s="285"/>
+      <c r="B20" s="286"/>
+      <c r="C20" s="286"/>
+      <c r="D20" s="286"/>
+      <c r="E20" s="286"/>
+      <c r="F20" s="286"/>
+      <c r="G20" s="286"/>
+      <c r="H20" s="286"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="286"/>
     </row>
     <row r="21" spans="1:10" ht="32.1" customHeight="1">
       <c r="A21" s="121" t="s">
@@ -11251,18 +11255,18 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="21.95" customHeight="1">
-      <c r="A39" s="310" t="s">
+      <c r="A39" s="287" t="s">
         <v>1295</v>
       </c>
-      <c r="B39" s="285"/>
-      <c r="C39" s="285"/>
-      <c r="D39" s="285"/>
-      <c r="E39" s="285"/>
-      <c r="F39" s="285"/>
-      <c r="G39" s="285"/>
-      <c r="H39" s="285"/>
-      <c r="I39" s="285"/>
-      <c r="J39" s="285"/>
+      <c r="B39" s="286"/>
+      <c r="C39" s="286"/>
+      <c r="D39" s="286"/>
+      <c r="E39" s="286"/>
+      <c r="F39" s="286"/>
+      <c r="G39" s="286"/>
+      <c r="H39" s="286"/>
+      <c r="I39" s="286"/>
+      <c r="J39" s="286"/>
     </row>
     <row r="40" spans="1:10" ht="32.1" customHeight="1">
       <c r="A40" s="129" t="s">
@@ -11422,49 +11426,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>1326</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
     </row>
     <row r="2" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A2" s="338" t="s">
+      <c r="A2" s="339" t="s">
         <v>1327</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
+      <c r="K2" s="286"/>
     </row>
     <row r="4" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A4" s="297" t="s">
+      <c r="A4" s="288" t="s">
         <v>1328</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
+      <c r="K4" s="286"/>
     </row>
     <row r="5" spans="1:11" ht="32.1" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -11659,19 +11663,19 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A11" s="313" t="s">
+      <c r="A11" s="289" t="s">
         <v>1344</v>
       </c>
-      <c r="B11" s="285"/>
-      <c r="C11" s="285"/>
-      <c r="D11" s="285"/>
-      <c r="E11" s="285"/>
-      <c r="F11" s="285"/>
-      <c r="G11" s="285"/>
-      <c r="H11" s="285"/>
-      <c r="I11" s="285"/>
-      <c r="J11" s="285"/>
-      <c r="K11" s="285"/>
+      <c r="B11" s="286"/>
+      <c r="C11" s="286"/>
+      <c r="D11" s="286"/>
+      <c r="E11" s="286"/>
+      <c r="F11" s="286"/>
+      <c r="G11" s="286"/>
+      <c r="H11" s="286"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="286"/>
+      <c r="K11" s="286"/>
     </row>
     <row r="12" spans="1:11" ht="32.1" customHeight="1">
       <c r="A12" s="121" t="s">
@@ -11894,19 +11898,19 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A23" s="310" t="s">
+      <c r="A23" s="287" t="s">
         <v>1375</v>
       </c>
-      <c r="B23" s="285"/>
-      <c r="C23" s="285"/>
-      <c r="D23" s="285"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="285"/>
-      <c r="J23" s="285"/>
-      <c r="K23" s="285"/>
+      <c r="B23" s="286"/>
+      <c r="C23" s="286"/>
+      <c r="D23" s="286"/>
+      <c r="E23" s="286"/>
+      <c r="F23" s="286"/>
+      <c r="G23" s="286"/>
+      <c r="H23" s="286"/>
+      <c r="I23" s="286"/>
+      <c r="J23" s="286"/>
+      <c r="K23" s="286"/>
     </row>
     <row r="24" spans="1:11" ht="32.1" customHeight="1">
       <c r="A24" s="129" t="s">
@@ -12088,19 +12092,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A31" s="297" t="s">
+      <c r="A31" s="288" t="s">
         <v>1384</v>
       </c>
-      <c r="B31" s="285"/>
-      <c r="C31" s="285"/>
-      <c r="D31" s="285"/>
-      <c r="E31" s="285"/>
-      <c r="F31" s="285"/>
-      <c r="G31" s="285"/>
-      <c r="H31" s="285"/>
-      <c r="I31" s="285"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="285"/>
+      <c r="B31" s="286"/>
+      <c r="C31" s="286"/>
+      <c r="D31" s="286"/>
+      <c r="E31" s="286"/>
+      <c r="F31" s="286"/>
+      <c r="G31" s="286"/>
+      <c r="H31" s="286"/>
+      <c r="I31" s="286"/>
+      <c r="J31" s="286"/>
+      <c r="K31" s="286"/>
     </row>
     <row r="32" spans="1:11" ht="32.1" customHeight="1">
       <c r="A32" s="33" t="s">
@@ -12270,45 +12274,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>1409</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="2" spans="1:17" ht="21.95" customHeight="1">
-      <c r="A2" s="340" t="s">
+      <c r="A2" s="341" t="s">
         <v>1410</v>
       </c>
-      <c r="B2" s="303"/>
-      <c r="C2" s="303"/>
-      <c r="D2" s="303"/>
-      <c r="E2" s="303"/>
-      <c r="F2" s="303"/>
-      <c r="G2" s="303"/>
-      <c r="H2" s="303"/>
-      <c r="I2" s="303"/>
-      <c r="J2" s="303"/>
-      <c r="K2" s="303"/>
-      <c r="L2" s="303"/>
-      <c r="M2" s="303"/>
-      <c r="N2" s="303"/>
-      <c r="O2" s="303"/>
-      <c r="P2" s="303"/>
-      <c r="Q2" s="289"/>
+      <c r="B2" s="295"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="295"/>
+      <c r="H2" s="295"/>
+      <c r="I2" s="295"/>
+      <c r="J2" s="295"/>
+      <c r="K2" s="295"/>
+      <c r="L2" s="295"/>
+      <c r="M2" s="295"/>
+      <c r="N2" s="295"/>
+      <c r="O2" s="295"/>
+      <c r="P2" s="295"/>
+      <c r="Q2" s="293"/>
     </row>
     <row r="3" spans="1:17" ht="25.5" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -13060,172 +13064,172 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="297" t="s">
+      <c r="A17" s="288" t="s">
         <v>1424</v>
       </c>
-      <c r="B17" s="285"/>
-      <c r="C17" s="285"/>
-      <c r="D17" s="285"/>
-      <c r="E17" s="285"/>
-      <c r="F17" s="285"/>
-      <c r="G17" s="285"/>
-      <c r="H17" s="285"/>
-      <c r="I17" s="285"/>
-      <c r="J17" s="285"/>
-      <c r="K17" s="285"/>
-      <c r="L17" s="285"/>
-      <c r="M17" s="285"/>
-      <c r="N17" s="285"/>
-      <c r="O17" s="285"/>
-      <c r="P17" s="285"/>
-      <c r="Q17" s="285"/>
+      <c r="B17" s="286"/>
+      <c r="C17" s="286"/>
+      <c r="D17" s="286"/>
+      <c r="E17" s="286"/>
+      <c r="F17" s="286"/>
+      <c r="G17" s="286"/>
+      <c r="H17" s="286"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="286"/>
+      <c r="K17" s="286"/>
+      <c r="L17" s="286"/>
+      <c r="M17" s="286"/>
+      <c r="N17" s="286"/>
+      <c r="O17" s="286"/>
+      <c r="P17" s="286"/>
+      <c r="Q17" s="286"/>
     </row>
     <row r="18" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A18" s="309" t="s">
+      <c r="A18" s="313" t="s">
         <v>1425</v>
       </c>
-      <c r="B18" s="303"/>
-      <c r="C18" s="303"/>
-      <c r="D18" s="303"/>
-      <c r="E18" s="303"/>
-      <c r="F18" s="303"/>
-      <c r="G18" s="303"/>
-      <c r="H18" s="303"/>
-      <c r="I18" s="303"/>
-      <c r="J18" s="303"/>
-      <c r="K18" s="303"/>
-      <c r="L18" s="303"/>
-      <c r="M18" s="303"/>
-      <c r="N18" s="303"/>
-      <c r="O18" s="303"/>
-      <c r="P18" s="303"/>
-      <c r="Q18" s="289"/>
+      <c r="B18" s="295"/>
+      <c r="C18" s="295"/>
+      <c r="D18" s="295"/>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="295"/>
+      <c r="I18" s="295"/>
+      <c r="J18" s="295"/>
+      <c r="K18" s="295"/>
+      <c r="L18" s="295"/>
+      <c r="M18" s="295"/>
+      <c r="N18" s="295"/>
+      <c r="O18" s="295"/>
+      <c r="P18" s="295"/>
+      <c r="Q18" s="293"/>
     </row>
     <row r="19" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A19" s="308" t="s">
+      <c r="A19" s="312" t="s">
         <v>1426</v>
       </c>
-      <c r="B19" s="303"/>
-      <c r="C19" s="303"/>
-      <c r="D19" s="303"/>
-      <c r="E19" s="303"/>
-      <c r="F19" s="303"/>
-      <c r="G19" s="303"/>
-      <c r="H19" s="303"/>
-      <c r="I19" s="303"/>
-      <c r="J19" s="303"/>
-      <c r="K19" s="303"/>
-      <c r="L19" s="303"/>
-      <c r="M19" s="303"/>
-      <c r="N19" s="303"/>
-      <c r="O19" s="303"/>
-      <c r="P19" s="303"/>
-      <c r="Q19" s="289"/>
+      <c r="B19" s="295"/>
+      <c r="C19" s="295"/>
+      <c r="D19" s="295"/>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="295"/>
+      <c r="I19" s="295"/>
+      <c r="J19" s="295"/>
+      <c r="K19" s="295"/>
+      <c r="L19" s="295"/>
+      <c r="M19" s="295"/>
+      <c r="N19" s="295"/>
+      <c r="O19" s="295"/>
+      <c r="P19" s="295"/>
+      <c r="Q19" s="293"/>
     </row>
     <row r="20" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A20" s="309" t="s">
+      <c r="A20" s="313" t="s">
         <v>1427</v>
       </c>
-      <c r="B20" s="303"/>
-      <c r="C20" s="303"/>
-      <c r="D20" s="303"/>
-      <c r="E20" s="303"/>
-      <c r="F20" s="303"/>
-      <c r="G20" s="303"/>
-      <c r="H20" s="303"/>
-      <c r="I20" s="303"/>
-      <c r="J20" s="303"/>
-      <c r="K20" s="303"/>
-      <c r="L20" s="303"/>
-      <c r="M20" s="303"/>
-      <c r="N20" s="303"/>
-      <c r="O20" s="303"/>
-      <c r="P20" s="303"/>
-      <c r="Q20" s="289"/>
+      <c r="B20" s="295"/>
+      <c r="C20" s="295"/>
+      <c r="D20" s="295"/>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="295"/>
+      <c r="I20" s="295"/>
+      <c r="J20" s="295"/>
+      <c r="K20" s="295"/>
+      <c r="L20" s="295"/>
+      <c r="M20" s="295"/>
+      <c r="N20" s="295"/>
+      <c r="O20" s="295"/>
+      <c r="P20" s="295"/>
+      <c r="Q20" s="293"/>
     </row>
     <row r="21" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A21" s="308" t="s">
+      <c r="A21" s="312" t="s">
         <v>1428</v>
       </c>
-      <c r="B21" s="303"/>
-      <c r="C21" s="303"/>
-      <c r="D21" s="303"/>
-      <c r="E21" s="303"/>
-      <c r="F21" s="303"/>
-      <c r="G21" s="303"/>
-      <c r="H21" s="303"/>
-      <c r="I21" s="303"/>
-      <c r="J21" s="303"/>
-      <c r="K21" s="303"/>
-      <c r="L21" s="303"/>
-      <c r="M21" s="303"/>
-      <c r="N21" s="303"/>
-      <c r="O21" s="303"/>
-      <c r="P21" s="303"/>
-      <c r="Q21" s="289"/>
+      <c r="B21" s="295"/>
+      <c r="C21" s="295"/>
+      <c r="D21" s="295"/>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="295"/>
+      <c r="I21" s="295"/>
+      <c r="J21" s="295"/>
+      <c r="K21" s="295"/>
+      <c r="L21" s="295"/>
+      <c r="M21" s="295"/>
+      <c r="N21" s="295"/>
+      <c r="O21" s="295"/>
+      <c r="P21" s="295"/>
+      <c r="Q21" s="293"/>
     </row>
     <row r="22" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A22" s="309" t="s">
+      <c r="A22" s="313" t="s">
         <v>1429</v>
       </c>
-      <c r="B22" s="303"/>
-      <c r="C22" s="303"/>
-      <c r="D22" s="303"/>
-      <c r="E22" s="303"/>
-      <c r="F22" s="303"/>
-      <c r="G22" s="303"/>
-      <c r="H22" s="303"/>
-      <c r="I22" s="303"/>
-      <c r="J22" s="303"/>
-      <c r="K22" s="303"/>
-      <c r="L22" s="303"/>
-      <c r="M22" s="303"/>
-      <c r="N22" s="303"/>
-      <c r="O22" s="303"/>
-      <c r="P22" s="303"/>
-      <c r="Q22" s="289"/>
+      <c r="B22" s="295"/>
+      <c r="C22" s="295"/>
+      <c r="D22" s="295"/>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
+      <c r="I22" s="295"/>
+      <c r="J22" s="295"/>
+      <c r="K22" s="295"/>
+      <c r="L22" s="295"/>
+      <c r="M22" s="295"/>
+      <c r="N22" s="295"/>
+      <c r="O22" s="295"/>
+      <c r="P22" s="295"/>
+      <c r="Q22" s="293"/>
     </row>
     <row r="23" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A23" s="308" t="s">
+      <c r="A23" s="312" t="s">
         <v>1430</v>
       </c>
-      <c r="B23" s="303"/>
-      <c r="C23" s="303"/>
-      <c r="D23" s="303"/>
-      <c r="E23" s="303"/>
-      <c r="F23" s="303"/>
-      <c r="G23" s="303"/>
-      <c r="H23" s="303"/>
-      <c r="I23" s="303"/>
-      <c r="J23" s="303"/>
-      <c r="K23" s="303"/>
-      <c r="L23" s="303"/>
-      <c r="M23" s="303"/>
-      <c r="N23" s="303"/>
-      <c r="O23" s="303"/>
-      <c r="P23" s="303"/>
-      <c r="Q23" s="289"/>
+      <c r="B23" s="295"/>
+      <c r="C23" s="295"/>
+      <c r="D23" s="295"/>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="295"/>
+      <c r="I23" s="295"/>
+      <c r="J23" s="295"/>
+      <c r="K23" s="295"/>
+      <c r="L23" s="295"/>
+      <c r="M23" s="295"/>
+      <c r="N23" s="295"/>
+      <c r="O23" s="295"/>
+      <c r="P23" s="295"/>
+      <c r="Q23" s="293"/>
     </row>
     <row r="24" spans="1:17" ht="27.95" customHeight="1">
-      <c r="A24" s="339" t="s">
+      <c r="A24" s="340" t="s">
         <v>1431</v>
       </c>
-      <c r="B24" s="303"/>
-      <c r="C24" s="303"/>
-      <c r="D24" s="303"/>
-      <c r="E24" s="303"/>
-      <c r="F24" s="303"/>
-      <c r="G24" s="303"/>
-      <c r="H24" s="303"/>
-      <c r="I24" s="303"/>
-      <c r="J24" s="303"/>
-      <c r="K24" s="303"/>
-      <c r="L24" s="303"/>
-      <c r="M24" s="303"/>
-      <c r="N24" s="303"/>
-      <c r="O24" s="303"/>
-      <c r="P24" s="303"/>
-      <c r="Q24" s="289"/>
+      <c r="B24" s="295"/>
+      <c r="C24" s="295"/>
+      <c r="D24" s="295"/>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="295"/>
+      <c r="K24" s="295"/>
+      <c r="L24" s="295"/>
+      <c r="M24" s="295"/>
+      <c r="N24" s="295"/>
+      <c r="O24" s="295"/>
+      <c r="P24" s="295"/>
+      <c r="Q24" s="293"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13262,175 +13266,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="287" t="s">
+      <c r="A2" s="306" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
-      <c r="M2" s="285"/>
-      <c r="N2" s="285"/>
-      <c r="O2" s="285"/>
-      <c r="P2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
+      <c r="K2" s="286"/>
+      <c r="L2" s="286"/>
+      <c r="M2" s="286"/>
+      <c r="N2" s="286"/>
+      <c r="O2" s="286"/>
+      <c r="P2" s="286"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="D4" s="284" t="s">
+      <c r="B4" s="286"/>
+      <c r="D4" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="285"/>
-      <c r="G4" s="284" t="s">
+      <c r="E4" s="286"/>
+      <c r="G4" s="304" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="285"/>
-      <c r="J4" s="284" t="s">
+      <c r="H4" s="286"/>
+      <c r="J4" s="304" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="285"/>
-      <c r="M4" s="284" t="s">
+      <c r="K4" s="286"/>
+      <c r="M4" s="304" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="285"/>
+      <c r="N4" s="286"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="293" t="s">
+      <c r="A5" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="285"/>
-      <c r="D5" s="293" t="s">
+      <c r="B5" s="286"/>
+      <c r="D5" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="285"/>
-      <c r="G5" s="293" t="s">
+      <c r="E5" s="286"/>
+      <c r="G5" s="303" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="285"/>
-      <c r="J5" s="293" t="s">
+      <c r="H5" s="286"/>
+      <c r="J5" s="303" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="285"/>
-      <c r="M5" s="293" t="s">
+      <c r="K5" s="286"/>
+      <c r="M5" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="285"/>
+      <c r="N5" s="286"/>
     </row>
     <row r="6" spans="1:16" ht="36" customHeight="1">
-      <c r="A6" s="304" t="s">
+      <c r="A6" s="296" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="285"/>
-      <c r="D6" s="305" t="s">
+      <c r="B6" s="286"/>
+      <c r="D6" s="297" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="285"/>
-      <c r="G6" s="304" t="s">
+      <c r="E6" s="286"/>
+      <c r="G6" s="296" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="285"/>
-      <c r="J6" s="291" t="s">
+      <c r="H6" s="286"/>
+      <c r="J6" s="299" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="285"/>
-      <c r="M6" s="291" t="s">
+      <c r="K6" s="286"/>
+      <c r="M6" s="299" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="285"/>
+      <c r="N6" s="286"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="290" t="s">
+      <c r="A7" s="302" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="285"/>
-      <c r="D7" s="290" t="s">
+      <c r="B7" s="286"/>
+      <c r="D7" s="302" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="285"/>
-      <c r="G7" s="290" t="s">
+      <c r="E7" s="286"/>
+      <c r="G7" s="302" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="285"/>
-      <c r="J7" s="290" t="s">
+      <c r="H7" s="286"/>
+      <c r="J7" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="285"/>
-      <c r="M7" s="290" t="s">
+      <c r="K7" s="286"/>
+      <c r="M7" s="302" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="285"/>
+      <c r="N7" s="286"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="294" t="s">
+      <c r="A8" s="291" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="285"/>
-      <c r="D8" s="296" t="s">
+      <c r="B8" s="286"/>
+      <c r="D8" s="307" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="285"/>
-      <c r="G8" s="294" t="s">
+      <c r="E8" s="286"/>
+      <c r="G8" s="291" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="285"/>
-      <c r="J8" s="295" t="s">
+      <c r="H8" s="286"/>
+      <c r="J8" s="301" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="285"/>
-      <c r="M8" s="295" t="s">
+      <c r="K8" s="286"/>
+      <c r="M8" s="301" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="285"/>
+      <c r="N8" s="286"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="297" t="s">
+      <c r="A10" s="288" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="285"/>
-      <c r="C10" s="285"/>
-      <c r="D10" s="285"/>
-      <c r="E10" s="285"/>
-      <c r="F10" s="285"/>
-      <c r="G10" s="285"/>
-      <c r="H10" s="285"/>
-      <c r="J10" s="300" t="s">
+      <c r="B10" s="286"/>
+      <c r="C10" s="286"/>
+      <c r="D10" s="286"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="286"/>
+      <c r="H10" s="286"/>
+      <c r="J10" s="310" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
+      <c r="K10" s="286"/>
+      <c r="L10" s="286"/>
+      <c r="M10" s="286"/>
+      <c r="N10" s="286"/>
+      <c r="O10" s="286"/>
+      <c r="P10" s="286"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
@@ -13457,17 +13461,17 @@
       <c r="H11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="288" t="s">
+      <c r="J11" s="292" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="289"/>
-      <c r="L11" s="302" t="s">
+      <c r="K11" s="293"/>
+      <c r="L11" s="294" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="303"/>
-      <c r="N11" s="303"/>
-      <c r="O11" s="303"/>
-      <c r="P11" s="289"/>
+      <c r="M11" s="295"/>
+      <c r="N11" s="295"/>
+      <c r="O11" s="295"/>
+      <c r="P11" s="293"/>
     </row>
     <row r="12" spans="1:16" ht="63.75" customHeight="1">
       <c r="A12" s="4" t="s">
@@ -13495,17 +13499,17 @@
       <c r="H12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="301" t="s">
+      <c r="J12" s="300" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="289"/>
-      <c r="L12" s="306" t="s">
+      <c r="K12" s="293"/>
+      <c r="L12" s="298" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="303"/>
-      <c r="N12" s="303"/>
-      <c r="O12" s="303"/>
-      <c r="P12" s="289"/>
+      <c r="M12" s="295"/>
+      <c r="N12" s="295"/>
+      <c r="O12" s="295"/>
+      <c r="P12" s="293"/>
     </row>
     <row r="13" spans="1:16" ht="63.75" customHeight="1">
       <c r="A13" s="3" t="s">
@@ -13533,23 +13537,23 @@
       <c r="H13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="288" t="s">
+      <c r="J13" s="292" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="289"/>
-      <c r="L13" s="302" t="s">
+      <c r="K13" s="293"/>
+      <c r="L13" s="294" t="s">
         <v>43</v>
       </c>
-      <c r="M13" s="303"/>
-      <c r="N13" s="303"/>
-      <c r="O13" s="303"/>
-      <c r="P13" s="289"/>
+      <c r="M13" s="295"/>
+      <c r="N13" s="295"/>
+      <c r="O13" s="295"/>
+      <c r="P13" s="293"/>
     </row>
     <row r="14" spans="1:16" ht="38.25" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="341">
+      <c r="B14" s="284">
         <v>0.192</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -13570,17 +13574,17 @@
       <c r="H14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="301" t="s">
+      <c r="J14" s="300" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="289"/>
-      <c r="L14" s="306" t="s">
+      <c r="K14" s="293"/>
+      <c r="L14" s="298" t="s">
         <v>52</v>
       </c>
-      <c r="M14" s="303"/>
-      <c r="N14" s="303"/>
-      <c r="O14" s="303"/>
-      <c r="P14" s="289"/>
+      <c r="M14" s="295"/>
+      <c r="N14" s="295"/>
+      <c r="O14" s="295"/>
+      <c r="P14" s="293"/>
     </row>
     <row r="15" spans="1:16" ht="63.75" customHeight="1">
       <c r="A15" s="3" t="s">
@@ -13608,17 +13612,17 @@
       <c r="H15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="288" t="s">
+      <c r="J15" s="292" t="s">
         <v>54</v>
       </c>
-      <c r="K15" s="289"/>
-      <c r="L15" s="302" t="s">
+      <c r="K15" s="293"/>
+      <c r="L15" s="294" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="303"/>
-      <c r="N15" s="303"/>
-      <c r="O15" s="303"/>
-      <c r="P15" s="289"/>
+      <c r="M15" s="295"/>
+      <c r="N15" s="295"/>
+      <c r="O15" s="295"/>
+      <c r="P15" s="293"/>
     </row>
     <row r="16" spans="1:16" ht="63.75" customHeight="1">
       <c r="A16" s="4" t="s">
@@ -13646,17 +13650,17 @@
       <c r="H16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J16" s="301" t="s">
+      <c r="J16" s="300" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="289"/>
-      <c r="L16" s="306" t="s">
+      <c r="K16" s="293"/>
+      <c r="L16" s="298" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="303"/>
-      <c r="N16" s="303"/>
-      <c r="O16" s="303"/>
-      <c r="P16" s="289"/>
+      <c r="M16" s="295"/>
+      <c r="N16" s="295"/>
+      <c r="O16" s="295"/>
+      <c r="P16" s="293"/>
     </row>
     <row r="17" spans="1:16" ht="38.25" customHeight="1">
       <c r="A17" s="3" t="s">
@@ -13684,17 +13688,17 @@
       <c r="H17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="288" t="s">
+      <c r="J17" s="292" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="289"/>
-      <c r="L17" s="302" t="s">
+      <c r="K17" s="293"/>
+      <c r="L17" s="294" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="303"/>
-      <c r="N17" s="303"/>
-      <c r="O17" s="303"/>
-      <c r="P17" s="289"/>
+      <c r="M17" s="295"/>
+      <c r="N17" s="295"/>
+      <c r="O17" s="295"/>
+      <c r="P17" s="293"/>
     </row>
     <row r="18" spans="1:16" ht="25.5" customHeight="1">
       <c r="A18" s="4" t="s">
@@ -13722,59 +13726,93 @@
       <c r="H18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="301" t="s">
+      <c r="J18" s="300" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="289"/>
-      <c r="L18" s="306" t="s">
+      <c r="K18" s="293"/>
+      <c r="L18" s="298" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="303"/>
-      <c r="N18" s="303"/>
-      <c r="O18" s="303"/>
-      <c r="P18" s="289"/>
+      <c r="M18" s="295"/>
+      <c r="N18" s="295"/>
+      <c r="O18" s="295"/>
+      <c r="P18" s="293"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="J19" s="288" t="s">
+      <c r="J19" s="292" t="s">
         <v>68</v>
       </c>
-      <c r="K19" s="289"/>
-      <c r="L19" s="302" t="s">
+      <c r="K19" s="293"/>
+      <c r="L19" s="294" t="s">
         <v>69</v>
       </c>
-      <c r="M19" s="303"/>
-      <c r="N19" s="303"/>
-      <c r="O19" s="303"/>
-      <c r="P19" s="289"/>
+      <c r="M19" s="295"/>
+      <c r="N19" s="295"/>
+      <c r="O19" s="295"/>
+      <c r="P19" s="293"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="298" t="s">
+      <c r="B21" s="308" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="285"/>
+      <c r="C21" s="286"/>
       <c r="D21" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="286" t="s">
+      <c r="E21" s="305" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="285"/>
+      <c r="F21" s="286"/>
       <c r="G21" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="299" t="s">
+      <c r="H21" s="309" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="285"/>
+      <c r="I21" s="286"/>
       <c r="J21" s="11" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="L13:P13"/>
@@ -13791,40 +13829,6 @@
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L16:P16"/>
     <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L11:P11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J10:P10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13848,28 +13852,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="311" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
     </row>
     <row r="3" spans="1:8" ht="36" customHeight="1">
       <c r="A3" s="1"/>
@@ -14668,26 +14672,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="311" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1">
       <c r="A3" s="1"/>
@@ -15428,15 +15432,15 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="297" t="s">
+      <c r="A41" s="288" t="s">
         <v>250</v>
       </c>
-      <c r="B41" s="285"/>
-      <c r="C41" s="285"/>
-      <c r="D41" s="285"/>
-      <c r="E41" s="285"/>
-      <c r="F41" s="285"/>
-      <c r="G41" s="285"/>
+      <c r="B41" s="286"/>
+      <c r="C41" s="286"/>
+      <c r="D41" s="286"/>
+      <c r="E41" s="286"/>
+      <c r="F41" s="286"/>
+      <c r="G41" s="286"/>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="12"/>
@@ -15842,49 +15846,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
     </row>
     <row r="2" spans="1:11" ht="32.1" customHeight="1">
-      <c r="A2" s="311" t="s">
+      <c r="A2" s="315" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
+      <c r="K2" s="286"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="297" t="s">
+      <c r="A4" s="288" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
+      <c r="K4" s="286"/>
     </row>
     <row r="5" spans="1:11" ht="32.1" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -16211,19 +16215,19 @@
       <c r="K13" s="91"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="313" t="s">
+      <c r="A15" s="289" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="285"/>
-      <c r="C15" s="285"/>
-      <c r="D15" s="285"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="285"/>
-      <c r="G15" s="285"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="285"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="285"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
+      <c r="H15" s="286"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="286"/>
+      <c r="K15" s="286"/>
     </row>
     <row r="16" spans="1:11" ht="32.1" customHeight="1">
       <c r="A16" s="121" t="s">
@@ -16264,11 +16268,11 @@
       <c r="F17" s="314" t="s">
         <v>322</v>
       </c>
-      <c r="G17" s="303"/>
-      <c r="H17" s="303"/>
-      <c r="I17" s="303"/>
-      <c r="J17" s="303"/>
-      <c r="K17" s="289"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="295"/>
+      <c r="I17" s="295"/>
+      <c r="J17" s="295"/>
+      <c r="K17" s="293"/>
     </row>
     <row r="18" spans="1:11" ht="39" customHeight="1">
       <c r="A18" s="126" t="s">
@@ -16285,14 +16289,14 @@
         <v>93900</v>
       </c>
       <c r="E18" s="96"/>
-      <c r="F18" s="309" t="s">
+      <c r="F18" s="313" t="s">
         <v>325</v>
       </c>
-      <c r="G18" s="303"/>
-      <c r="H18" s="303"/>
-      <c r="I18" s="303"/>
-      <c r="J18" s="303"/>
-      <c r="K18" s="289"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="295"/>
+      <c r="I18" s="295"/>
+      <c r="J18" s="295"/>
+      <c r="K18" s="293"/>
     </row>
     <row r="19" spans="1:11" ht="39" customHeight="1">
       <c r="A19" s="127" t="s">
@@ -16309,14 +16313,14 @@
         <v>99000</v>
       </c>
       <c r="E19" s="92"/>
-      <c r="F19" s="308" t="s">
+      <c r="F19" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="G19" s="303"/>
-      <c r="H19" s="303"/>
-      <c r="I19" s="303"/>
-      <c r="J19" s="303"/>
-      <c r="K19" s="289"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="295"/>
+      <c r="I19" s="295"/>
+      <c r="J19" s="295"/>
+      <c r="K19" s="293"/>
     </row>
     <row r="20" spans="1:11" ht="39" customHeight="1">
       <c r="A20" s="126" t="s">
@@ -16333,14 +16337,14 @@
         <v>104450</v>
       </c>
       <c r="E20" s="96"/>
-      <c r="F20" s="309" t="s">
+      <c r="F20" s="313" t="s">
         <v>331</v>
       </c>
-      <c r="G20" s="303"/>
-      <c r="H20" s="303"/>
-      <c r="I20" s="303"/>
-      <c r="J20" s="303"/>
-      <c r="K20" s="289"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="295"/>
+      <c r="I20" s="295"/>
+      <c r="J20" s="295"/>
+      <c r="K20" s="293"/>
     </row>
     <row r="21" spans="1:11" ht="39" customHeight="1">
       <c r="A21" s="127" t="s">
@@ -16357,14 +16361,14 @@
         <v>107130</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="308" t="s">
+      <c r="F21" s="312" t="s">
         <v>334</v>
       </c>
-      <c r="G21" s="303"/>
-      <c r="H21" s="303"/>
-      <c r="I21" s="303"/>
-      <c r="J21" s="303"/>
-      <c r="K21" s="289"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="295"/>
+      <c r="I21" s="295"/>
+      <c r="J21" s="295"/>
+      <c r="K21" s="293"/>
     </row>
     <row r="22" spans="1:11" ht="39" customHeight="1">
       <c r="A22" s="126" t="s">
@@ -16381,14 +16385,14 @@
         <v>102930</v>
       </c>
       <c r="E22" s="96"/>
-      <c r="F22" s="309" t="s">
+      <c r="F22" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="G22" s="303"/>
-      <c r="H22" s="303"/>
-      <c r="I22" s="303"/>
-      <c r="J22" s="303"/>
-      <c r="K22" s="289"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
+      <c r="I22" s="295"/>
+      <c r="J22" s="295"/>
+      <c r="K22" s="293"/>
     </row>
     <row r="23" spans="1:11" ht="39" customHeight="1">
       <c r="A23" s="127" t="s">
@@ -16405,14 +16409,14 @@
         <v>100200</v>
       </c>
       <c r="E23" s="92"/>
-      <c r="F23" s="308" t="s">
+      <c r="F23" s="312" t="s">
         <v>340</v>
       </c>
-      <c r="G23" s="303"/>
-      <c r="H23" s="303"/>
-      <c r="I23" s="303"/>
-      <c r="J23" s="303"/>
-      <c r="K23" s="289"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="295"/>
+      <c r="I23" s="295"/>
+      <c r="J23" s="295"/>
+      <c r="K23" s="293"/>
     </row>
     <row r="24" spans="1:11" ht="39" customHeight="1">
       <c r="A24" s="128" t="s">
@@ -16432,29 +16436,29 @@
       <c r="E24" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="312" t="s">
+      <c r="F24" s="316" t="s">
         <v>343</v>
       </c>
-      <c r="G24" s="303"/>
-      <c r="H24" s="303"/>
-      <c r="I24" s="303"/>
-      <c r="J24" s="303"/>
-      <c r="K24" s="289"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="295"/>
+      <c r="K24" s="293"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="310" t="s">
+      <c r="A27" s="287" t="s">
         <v>344</v>
       </c>
-      <c r="B27" s="285"/>
-      <c r="C27" s="285"/>
-      <c r="D27" s="285"/>
-      <c r="E27" s="285"/>
-      <c r="F27" s="285"/>
-      <c r="G27" s="285"/>
-      <c r="H27" s="285"/>
-      <c r="I27" s="285"/>
-      <c r="J27" s="285"/>
-      <c r="K27" s="285"/>
+      <c r="B27" s="286"/>
+      <c r="C27" s="286"/>
+      <c r="D27" s="286"/>
+      <c r="E27" s="286"/>
+      <c r="F27" s="286"/>
+      <c r="G27" s="286"/>
+      <c r="H27" s="286"/>
+      <c r="I27" s="286"/>
+      <c r="J27" s="286"/>
+      <c r="K27" s="286"/>
     </row>
     <row r="28" spans="1:11" ht="32.1" customHeight="1">
       <c r="A28" s="129" t="s">
@@ -16492,14 +16496,14 @@
       <c r="E29" s="92" t="s">
         <v>353</v>
       </c>
-      <c r="F29" s="308" t="s">
+      <c r="F29" s="312" t="s">
         <v>354</v>
       </c>
-      <c r="G29" s="303"/>
-      <c r="H29" s="303"/>
-      <c r="I29" s="303"/>
-      <c r="J29" s="303"/>
-      <c r="K29" s="289"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
+      <c r="I29" s="295"/>
+      <c r="J29" s="295"/>
+      <c r="K29" s="293"/>
     </row>
     <row r="30" spans="1:11" ht="26.25" customHeight="1">
       <c r="A30" s="4" t="s">
@@ -16517,14 +16521,14 @@
       <c r="E30" s="118">
         <v>2800</v>
       </c>
-      <c r="F30" s="309" t="s">
+      <c r="F30" s="313" t="s">
         <v>359</v>
       </c>
-      <c r="G30" s="303"/>
-      <c r="H30" s="303"/>
-      <c r="I30" s="303"/>
-      <c r="J30" s="303"/>
-      <c r="K30" s="289"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="295"/>
+      <c r="I30" s="295"/>
+      <c r="J30" s="295"/>
+      <c r="K30" s="293"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="3" t="s">
@@ -16542,14 +16546,14 @@
       <c r="E31" s="119">
         <v>2650</v>
       </c>
-      <c r="F31" s="308" t="s">
+      <c r="F31" s="312" t="s">
         <v>363</v>
       </c>
-      <c r="G31" s="303"/>
-      <c r="H31" s="303"/>
-      <c r="I31" s="303"/>
-      <c r="J31" s="303"/>
-      <c r="K31" s="289"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="295"/>
+      <c r="I31" s="295"/>
+      <c r="J31" s="295"/>
+      <c r="K31" s="293"/>
     </row>
     <row r="32" spans="1:11" ht="26.25" customHeight="1">
       <c r="A32" s="4" t="s">
@@ -16567,14 +16571,14 @@
       <c r="E32" s="96" t="s">
         <v>353</v>
       </c>
-      <c r="F32" s="309" t="s">
+      <c r="F32" s="313" t="s">
         <v>368</v>
       </c>
-      <c r="G32" s="303"/>
-      <c r="H32" s="303"/>
-      <c r="I32" s="303"/>
-      <c r="J32" s="303"/>
-      <c r="K32" s="289"/>
+      <c r="G32" s="295"/>
+      <c r="H32" s="295"/>
+      <c r="I32" s="295"/>
+      <c r="J32" s="295"/>
+      <c r="K32" s="293"/>
     </row>
     <row r="33" spans="1:11" ht="26.25" customHeight="1">
       <c r="A33" s="3" t="s">
@@ -16592,14 +16596,14 @@
       <c r="E33" s="119">
         <v>2900</v>
       </c>
-      <c r="F33" s="308" t="s">
+      <c r="F33" s="312" t="s">
         <v>371</v>
       </c>
-      <c r="G33" s="303"/>
-      <c r="H33" s="303"/>
-      <c r="I33" s="303"/>
-      <c r="J33" s="303"/>
-      <c r="K33" s="289"/>
+      <c r="G33" s="295"/>
+      <c r="H33" s="295"/>
+      <c r="I33" s="295"/>
+      <c r="J33" s="295"/>
+      <c r="K33" s="293"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
@@ -16617,14 +16621,14 @@
       <c r="E34" s="118">
         <v>1600</v>
       </c>
-      <c r="F34" s="309" t="s">
+      <c r="F34" s="313" t="s">
         <v>373</v>
       </c>
-      <c r="G34" s="303"/>
-      <c r="H34" s="303"/>
-      <c r="I34" s="303"/>
-      <c r="J34" s="303"/>
-      <c r="K34" s="289"/>
+      <c r="G34" s="295"/>
+      <c r="H34" s="295"/>
+      <c r="I34" s="295"/>
+      <c r="J34" s="295"/>
+      <c r="K34" s="293"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="3" t="s">
@@ -16642,14 +16646,14 @@
       <c r="E35" s="119">
         <v>3200</v>
       </c>
-      <c r="F35" s="308" t="s">
+      <c r="F35" s="312" t="s">
         <v>376</v>
       </c>
-      <c r="G35" s="303"/>
-      <c r="H35" s="303"/>
-      <c r="I35" s="303"/>
-      <c r="J35" s="303"/>
-      <c r="K35" s="289"/>
+      <c r="G35" s="295"/>
+      <c r="H35" s="295"/>
+      <c r="I35" s="295"/>
+      <c r="J35" s="295"/>
+      <c r="K35" s="293"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
@@ -16667,25 +16671,17 @@
       <c r="E36" s="118">
         <v>29900</v>
       </c>
-      <c r="F36" s="309" t="s">
+      <c r="F36" s="313" t="s">
         <v>380</v>
       </c>
-      <c r="G36" s="303"/>
-      <c r="H36" s="303"/>
-      <c r="I36" s="303"/>
-      <c r="J36" s="303"/>
-      <c r="K36" s="289"/>
+      <c r="G36" s="295"/>
+      <c r="H36" s="295"/>
+      <c r="I36" s="295"/>
+      <c r="J36" s="295"/>
+      <c r="K36" s="293"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="F36:K36"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="F35:K35"/>
-    <mergeCell ref="F34:K34"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="F23:K23"/>
     <mergeCell ref="F22:K22"/>
@@ -16699,6 +16695,14 @@
     <mergeCell ref="F21:K21"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="F20:K20"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="F36:K36"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="F18:K18"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="F35:K35"/>
+    <mergeCell ref="F34:K34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16723,46 +16727,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>381</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="311" t="s">
         <v>382</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="297" t="s">
+      <c r="A4" s="288" t="s">
         <v>383</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -16824,7 +16828,7 @@
       <c r="I6" s="224" t="s">
         <v>397</v>
       </c>
-      <c r="J6" s="316" t="s">
+      <c r="J6" s="317" t="s">
         <v>398</v>
       </c>
     </row>
@@ -16856,7 +16860,7 @@
       <c r="I7" s="131" t="s">
         <v>353</v>
       </c>
-      <c r="J7" s="308" t="s">
+      <c r="J7" s="312" t="s">
         <v>402</v>
       </c>
     </row>
@@ -16888,7 +16892,7 @@
       <c r="I8" s="132" t="s">
         <v>353</v>
       </c>
-      <c r="J8" s="309" t="s">
+      <c r="J8" s="313" t="s">
         <v>404</v>
       </c>
     </row>
@@ -16920,7 +16924,7 @@
       <c r="I9" s="131" t="s">
         <v>353</v>
       </c>
-      <c r="J9" s="308" t="s">
+      <c r="J9" s="312" t="s">
         <v>408</v>
       </c>
     </row>
@@ -16952,7 +16956,7 @@
       <c r="I10" s="132" t="s">
         <v>353</v>
       </c>
-      <c r="J10" s="309" t="s">
+      <c r="J10" s="313" t="s">
         <v>412</v>
       </c>
     </row>
@@ -16980,37 +16984,37 @@
       <c r="I11" s="135" t="s">
         <v>353</v>
       </c>
-      <c r="J11" s="312" t="s">
+      <c r="J11" s="316" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A13" s="315" t="s">
+      <c r="A13" s="318" t="s">
         <v>415</v>
       </c>
-      <c r="B13" s="303"/>
-      <c r="C13" s="303"/>
-      <c r="D13" s="303"/>
-      <c r="E13" s="303"/>
-      <c r="F13" s="303"/>
-      <c r="G13" s="303"/>
-      <c r="H13" s="303"/>
-      <c r="I13" s="303"/>
-      <c r="J13" s="289"/>
+      <c r="B13" s="295"/>
+      <c r="C13" s="295"/>
+      <c r="D13" s="295"/>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="295"/>
+      <c r="I13" s="295"/>
+      <c r="J13" s="293"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="313" t="s">
+      <c r="A15" s="289" t="s">
         <v>416</v>
       </c>
-      <c r="B15" s="285"/>
-      <c r="C15" s="285"/>
-      <c r="D15" s="285"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="285"/>
-      <c r="G15" s="285"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="285"/>
-      <c r="J15" s="285"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
+      <c r="H15" s="286"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="286"/>
     </row>
     <row r="16" spans="1:10" ht="32.1" customHeight="1">
       <c r="A16" s="121" t="s">
@@ -17223,18 +17227,18 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="310" t="s">
+      <c r="A26" s="287" t="s">
         <v>477</v>
       </c>
-      <c r="B26" s="285"/>
-      <c r="C26" s="285"/>
-      <c r="D26" s="285"/>
-      <c r="E26" s="285"/>
-      <c r="F26" s="285"/>
-      <c r="G26" s="285"/>
-      <c r="H26" s="285"/>
-      <c r="I26" s="285"/>
-      <c r="J26" s="285"/>
+      <c r="B26" s="286"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="286"/>
+      <c r="E26" s="286"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
+      <c r="H26" s="286"/>
+      <c r="I26" s="286"/>
+      <c r="J26" s="286"/>
     </row>
     <row r="27" spans="1:10" ht="32.1" customHeight="1">
       <c r="A27" s="129" t="s">
@@ -17508,6 +17512,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="J7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="J10"/>
+    <mergeCell ref="A13:J13"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="J9"/>
     <mergeCell ref="J8"/>
@@ -17515,11 +17524,6 @@
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="J11"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="J7"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="J10"/>
-    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17542,46 +17546,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>522</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="317" t="s">
+      <c r="A2" s="319" t="s">
         <v>523</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="319" t="s">
+      <c r="A4" s="321" t="s">
         <v>524</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1">
       <c r="A5" s="142" t="s">
@@ -17876,18 +17880,18 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="320" t="s">
+      <c r="A16" s="322" t="s">
         <v>582</v>
       </c>
-      <c r="B16" s="285"/>
-      <c r="C16" s="285"/>
-      <c r="D16" s="285"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="285"/>
-      <c r="G16" s="285"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="285"/>
-      <c r="J16" s="285"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="286"/>
     </row>
     <row r="17" spans="1:10" ht="32.1" customHeight="1">
       <c r="A17" s="145" t="s">
@@ -18077,18 +18081,18 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="318" t="s">
+      <c r="A27" s="320" t="s">
         <v>603</v>
       </c>
-      <c r="B27" s="285"/>
-      <c r="C27" s="285"/>
-      <c r="D27" s="285"/>
-      <c r="E27" s="285"/>
-      <c r="F27" s="285"/>
-      <c r="G27" s="285"/>
-      <c r="H27" s="285"/>
-      <c r="I27" s="285"/>
-      <c r="J27" s="285"/>
+      <c r="B27" s="286"/>
+      <c r="C27" s="286"/>
+      <c r="D27" s="286"/>
+      <c r="E27" s="286"/>
+      <c r="F27" s="286"/>
+      <c r="G27" s="286"/>
+      <c r="H27" s="286"/>
+      <c r="I27" s="286"/>
+      <c r="J27" s="286"/>
     </row>
     <row r="28" spans="1:10" ht="32.1" customHeight="1">
       <c r="A28" s="148" t="s">
@@ -18299,40 +18303,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
-      <c r="J1" s="285"/>
-      <c r="K1" s="285"/>
-      <c r="L1" s="285"/>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="2" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A2" s="311" t="s">
+      <c r="A2" s="315" t="s">
         <v>651</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
+      <c r="J2" s="286"/>
+      <c r="K2" s="286"/>
+      <c r="L2" s="286"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
@@ -18373,23 +18377,23 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="321" t="s">
+      <c r="B4" s="323" t="s">
         <v>664</v>
       </c>
-      <c r="C4" s="303"/>
-      <c r="D4" s="303"/>
-      <c r="E4" s="289"/>
-      <c r="F4" s="321" t="s">
+      <c r="C4" s="295"/>
+      <c r="D4" s="295"/>
+      <c r="E4" s="293"/>
+      <c r="F4" s="323" t="s">
         <v>665</v>
       </c>
-      <c r="G4" s="303"/>
-      <c r="H4" s="303"/>
-      <c r="I4" s="289"/>
-      <c r="J4" s="321" t="s">
+      <c r="G4" s="295"/>
+      <c r="H4" s="295"/>
+      <c r="I4" s="293"/>
+      <c r="J4" s="323" t="s">
         <v>666</v>
       </c>
-      <c r="K4" s="303"/>
-      <c r="L4" s="289"/>
+      <c r="K4" s="295"/>
+      <c r="L4" s="293"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="13" t="s">
@@ -19232,76 +19236,76 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="80.099999999999994" customHeight="1">
-      <c r="A31" s="322" t="s">
+      <c r="A31" s="324" t="s">
         <v>685</v>
       </c>
-      <c r="B31" s="285"/>
-      <c r="C31" s="285"/>
-      <c r="D31" s="285"/>
-      <c r="E31" s="285"/>
-      <c r="F31" s="285"/>
-      <c r="G31" s="285"/>
-      <c r="H31" s="285"/>
-      <c r="I31" s="285"/>
-      <c r="J31" s="285"/>
-      <c r="K31" s="285"/>
-      <c r="L31" s="285"/>
+      <c r="B31" s="286"/>
+      <c r="C31" s="286"/>
+      <c r="D31" s="286"/>
+      <c r="E31" s="286"/>
+      <c r="F31" s="286"/>
+      <c r="G31" s="286"/>
+      <c r="H31" s="286"/>
+      <c r="I31" s="286"/>
+      <c r="J31" s="286"/>
+      <c r="K31" s="286"/>
+      <c r="L31" s="286"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="285"/>
-      <c r="B32" s="285"/>
-      <c r="C32" s="285"/>
-      <c r="D32" s="285"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="285"/>
-      <c r="G32" s="285"/>
-      <c r="H32" s="285"/>
-      <c r="I32" s="285"/>
-      <c r="J32" s="285"/>
-      <c r="K32" s="285"/>
-      <c r="L32" s="285"/>
+      <c r="A32" s="286"/>
+      <c r="B32" s="286"/>
+      <c r="C32" s="286"/>
+      <c r="D32" s="286"/>
+      <c r="E32" s="286"/>
+      <c r="F32" s="286"/>
+      <c r="G32" s="286"/>
+      <c r="H32" s="286"/>
+      <c r="I32" s="286"/>
+      <c r="J32" s="286"/>
+      <c r="K32" s="286"/>
+      <c r="L32" s="286"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="285"/>
-      <c r="B33" s="285"/>
-      <c r="C33" s="285"/>
-      <c r="D33" s="285"/>
-      <c r="E33" s="285"/>
-      <c r="F33" s="285"/>
-      <c r="G33" s="285"/>
-      <c r="H33" s="285"/>
-      <c r="I33" s="285"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="285"/>
-      <c r="L33" s="285"/>
+      <c r="A33" s="286"/>
+      <c r="B33" s="286"/>
+      <c r="C33" s="286"/>
+      <c r="D33" s="286"/>
+      <c r="E33" s="286"/>
+      <c r="F33" s="286"/>
+      <c r="G33" s="286"/>
+      <c r="H33" s="286"/>
+      <c r="I33" s="286"/>
+      <c r="J33" s="286"/>
+      <c r="K33" s="286"/>
+      <c r="L33" s="286"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="285"/>
-      <c r="B34" s="285"/>
-      <c r="C34" s="285"/>
-      <c r="D34" s="285"/>
-      <c r="E34" s="285"/>
-      <c r="F34" s="285"/>
-      <c r="G34" s="285"/>
-      <c r="H34" s="285"/>
-      <c r="I34" s="285"/>
-      <c r="J34" s="285"/>
-      <c r="K34" s="285"/>
-      <c r="L34" s="285"/>
+      <c r="A34" s="286"/>
+      <c r="B34" s="286"/>
+      <c r="C34" s="286"/>
+      <c r="D34" s="286"/>
+      <c r="E34" s="286"/>
+      <c r="F34" s="286"/>
+      <c r="G34" s="286"/>
+      <c r="H34" s="286"/>
+      <c r="I34" s="286"/>
+      <c r="J34" s="286"/>
+      <c r="K34" s="286"/>
+      <c r="L34" s="286"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="285"/>
-      <c r="B35" s="285"/>
-      <c r="C35" s="285"/>
-      <c r="D35" s="285"/>
-      <c r="E35" s="285"/>
-      <c r="F35" s="285"/>
-      <c r="G35" s="285"/>
-      <c r="H35" s="285"/>
-      <c r="I35" s="285"/>
-      <c r="J35" s="285"/>
-      <c r="K35" s="285"/>
-      <c r="L35" s="285"/>
+      <c r="A35" s="286"/>
+      <c r="B35" s="286"/>
+      <c r="C35" s="286"/>
+      <c r="D35" s="286"/>
+      <c r="E35" s="286"/>
+      <c r="F35" s="286"/>
+      <c r="G35" s="286"/>
+      <c r="H35" s="286"/>
+      <c r="I35" s="286"/>
+      <c r="J35" s="286"/>
+      <c r="K35" s="286"/>
+      <c r="L35" s="286"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -19336,43 +19340,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="285" t="s">
         <v>686</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="285"/>
-      <c r="H1" s="285"/>
-      <c r="I1" s="285"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
     </row>
     <row r="2" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A2" s="323" t="s">
+      <c r="A2" s="290" t="s">
         <v>687</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
+      <c r="B2" s="286"/>
+      <c r="C2" s="286"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="286"/>
+      <c r="I2" s="286"/>
     </row>
     <row r="4" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A4" s="297" t="s">
+      <c r="A4" s="288" t="s">
         <v>688</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="C4" s="285"/>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
     </row>
     <row r="5" spans="1:9" ht="32.1" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -19681,17 +19685,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A16" s="313" t="s">
+      <c r="A16" s="289" t="s">
         <v>708</v>
       </c>
-      <c r="B16" s="285"/>
-      <c r="C16" s="285"/>
-      <c r="D16" s="285"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="285"/>
-      <c r="G16" s="285"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="285"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
     </row>
     <row r="17" spans="1:9" ht="32.1" customHeight="1">
       <c r="A17" s="121" t="s">
@@ -19904,55 +19908,55 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A26" s="310" t="s">
+      <c r="A26" s="287" t="s">
         <v>743</v>
       </c>
-      <c r="B26" s="285"/>
-      <c r="C26" s="285"/>
-      <c r="D26" s="285"/>
-      <c r="E26" s="285"/>
-      <c r="F26" s="285"/>
-      <c r="G26" s="285"/>
-      <c r="H26" s="285"/>
-      <c r="I26" s="285"/>
+      <c r="B26" s="286"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="286"/>
+      <c r="E26" s="286"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
+      <c r="H26" s="286"/>
+      <c r="I26" s="286"/>
     </row>
     <row r="27" spans="1:9" ht="56.25" customHeight="1">
-      <c r="A27" s="324" t="str">
+      <c r="A27" s="325" t="str">
         <f>"April 2025 EBITDA of $"&amp;TEXT(B13,"#,##0")&amp;"K ("&amp;TEXT(B13/B6,"0.0%")&amp;" EBITDA margin) was $"&amp;TEXT(ABS(D13),"#,##0")&amp;"K ("&amp;TEXT(ABS(D13/C13),"0.0%")&amp;") below budget of $"&amp;TEXT(C13,"#,##0")&amp;"K. Volume shortfall of $"&amp;TEXT(ABS(B6-C6),"#,##0")&amp;"K in net sales revenue ("&amp;TEXT(ABS((B6-C6)/C6),"0.0%")&amp;") reduced EBITDA by $"&amp;TEXT(ABS(C19),"#,##0")&amp;"K, consistent with Etex Group commentary on depressed Victorian new-build markets. Labour costs ran $"&amp;TEXT(ABS(C20),"#,##0")&amp;"K above budget (BGC integration transition headcount; restructure targeted June-25). Partially offset by SG&amp;A savings of $"&amp;TEXT(ABS(C22),"#,##0")&amp;"K through logistics route optimisation and controlled spending. Full-year EBITDA target of 18.5% remains achievable pending BGC volume ramp H2 2025."</f>
         <v>April 2025 EBITDA of $4,200K (10.9% EBITDA margin) was $100K (2.3%) below budget of $4,300K. Volume shortfall of $1,750K in net sales revenue (4.4%) reduced EBITDA by $187K, consistent with Etex Group commentary on depressed Victorian new-build markets. Labour costs ran $384K above budget (BGC integration transition headcount; restructure targeted June-25). Partially offset by SG&amp;A savings of $100K through logistics route optimisation and controlled spending. Full-year EBITDA target of 18.5% remains achievable pending BGC volume ramp H2 2025.</v>
       </c>
-      <c r="B27" s="325"/>
-      <c r="C27" s="325"/>
-      <c r="D27" s="325"/>
-      <c r="E27" s="325"/>
-      <c r="F27" s="325"/>
-      <c r="G27" s="325"/>
-      <c r="H27" s="325"/>
-      <c r="I27" s="326"/>
+      <c r="B27" s="326"/>
+      <c r="C27" s="326"/>
+      <c r="D27" s="326"/>
+      <c r="E27" s="326"/>
+      <c r="F27" s="326"/>
+      <c r="G27" s="326"/>
+      <c r="H27" s="326"/>
+      <c r="I27" s="327"/>
     </row>
     <row r="28" spans="1:9" ht="5.0999999999999996" customHeight="1">
-      <c r="A28" s="327"/>
-      <c r="B28" s="328"/>
-      <c r="C28" s="328"/>
-      <c r="D28" s="328"/>
-      <c r="E28" s="328"/>
-      <c r="F28" s="328"/>
-      <c r="G28" s="328"/>
-      <c r="H28" s="328"/>
-      <c r="I28" s="329"/>
+      <c r="A28" s="328"/>
+      <c r="B28" s="329"/>
+      <c r="C28" s="329"/>
+      <c r="D28" s="329"/>
+      <c r="E28" s="329"/>
+      <c r="F28" s="329"/>
+      <c r="G28" s="329"/>
+      <c r="H28" s="329"/>
+      <c r="I28" s="330"/>
     </row>
     <row r="29" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A29" s="300" t="s">
+      <c r="A29" s="310" t="s">
         <v>744</v>
       </c>
-      <c r="B29" s="285"/>
-      <c r="C29" s="285"/>
-      <c r="D29" s="285"/>
-      <c r="E29" s="285"/>
-      <c r="F29" s="285"/>
-      <c r="G29" s="285"/>
-      <c r="H29" s="285"/>
-      <c r="I29" s="285"/>
+      <c r="B29" s="286"/>
+      <c r="C29" s="286"/>
+      <c r="D29" s="286"/>
+      <c r="E29" s="286"/>
+      <c r="F29" s="286"/>
+      <c r="G29" s="286"/>
+      <c r="H29" s="286"/>
+      <c r="I29" s="286"/>
     </row>
     <row r="30" spans="1:9" ht="32.1" customHeight="1">
       <c r="A30" s="210" t="s">
